--- a/排课结果/软偏好修复明细.xlsx
+++ b/排课结果/软偏好修复明细.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>150000290.135</t>
+          <t>150000290.028</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -516,24 +516,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>软件学院</t>
+          <t>建筑与艺术设计学院</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>新新锋</t>
+          <t>新艺</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>xkp01050013</t>
+          <t>xkp01346002</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -552,12 +552,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>网安2401 网安2402 网安2403 网安2404 网安2405 网安2406 网安2407 网安2408</t>
+          <t>建筑类2401 建筑类2402 建筑类2403 建筑类2404 设计类2401 设计类2402 设计类2403 设计类2404 设计类2405 设计类2406 工设2401 工设2402 建筑类2405</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>周三（5-6节）</t>
+          <t>周五（5-6节）</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -572,12 +572,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>周三</t>
+          <t>周五</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>第7-8节</t>
+          <t>第3-4节</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -587,7 +587,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>150000290.160</t>
+          <t>150000290.032</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -597,48 +597,48 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>化学化工学院 资源环境学院 资源环境学院</t>
+          <t>软件学院</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>新瑞青</t>
+          <t>新艺</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>xkp01050063</t>
+          <t>xkp01346002</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>2205</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CLS1006</t>
+          <t>CLS1010</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>南校区</t>
+          <t>北校区</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>矿加2401 矿加卓2401 矿加卓2402 应化2401 应化2402 应化2403 化工2401 化工2402 化工2403 化工2404 储能2401 储能2402 储能2403 地质2401 地质2402 地质卓2401 地科2401 地科2402 地科2403 水文2401 水文2402 水文2403 勘查拔尖班2401 勘查清洁2401 勘查清洁2402 勘查战略2401 勘查战略2402 环境2401 环境2402 环境生态2401 环境生态2402</t>
+          <t>网安2401 网安2402 网安2403 网安2404 网安2405 网安2406 网安2407 网安2408</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>周四（3-4节）</t>
+          <t>周五（5-6节）</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>周四</t>
+          <t>周三</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>150000290.180</t>
+          <t>150000290.034</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -678,33 +678,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>数学与信息科学学院 安全科学与工程学院</t>
+          <t>土木工程学院 利莫瑞克国际学院</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>新真</t>
+          <t>新娜娜</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>xkp01050036</t>
+          <t>xkp01230661</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>2203</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CLS1006</t>
+          <t>CLS1009</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>安全卓2401 安全卓2402 安全卓2403 安全卓2404 安全卓2405 安全卓2406 安全卓2407 安全卓2408 安全卓2409 消防2401 消防2402 数学类2401 数学类2402 数学类2403 数学类2404 数学类2405 数学类2406 数学类2407</t>
+          <t>土木2401 土木2402 土木2403 土木2404 土木2405 土木2406 土木2407 地下2401 地下2402 地下2403 工管2401 工管2402 智能建造2401 智能建造2402 力学2401 力学2402 计算机（国）2401 计算机（国）2402 计算机（国）2403 计算机（国）2404 自动化（国）2401 自动化（国）2402 自动化（国）2403 自动化（国）2404</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>周四（5-6节）</t>
+          <t>周五（5-6节）</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>周四</t>
+          <t>周五</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>第7-8节</t>
+          <t>第3-4节</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -749,7 +749,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>150000290.218</t>
+          <t>150000290.057</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -759,17 +759,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>外国语学院 材料科学与工程学院</t>
+          <t>电气工程与自动化学院</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>新真</t>
+          <t>新枫</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>xkp01050036</t>
+          <t>xkp01050026</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -780,12 +780,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>2306</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CLS1005</t>
+          <t>CLS1014</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -795,12 +795,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>材科2401 材科2402 材科2403 材科2404 材科2405 材科2406 材科2407 材科2408 材科2409 材科2410 智能材料2401 智能材料2402 新能源2401 新能源2402 新能源2403 新能源2404 材控2401 材控2402 材控2403 材控2404 日语2401 英语2401 英语2402 英语2403 英语2404</t>
+          <t>电气学院，周一3.46</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>周五（3-4节）</t>
+          <t>周一（3-4节）</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>周五</t>
+          <t>周一</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>第7-8节</t>
+          <t>第5-6节</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -830,7 +830,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>150000290.221</t>
+          <t>150000290.102</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -840,33 +840,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>外国语学院 材料科学与工程学院</t>
+          <t>工商管理学院</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>新衍榛</t>
+          <t>新枫</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>xkp01050012</t>
+          <t>xkp01050026</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>2403</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CLS1007</t>
+          <t>CLS1016</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -876,12 +876,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>材科2401 材科2402 材科2403 材科2404 材科2405 材科2406 材科2407 材科2408 材科2409 材科2410 智能材料2401 智能材料2402 新能源2401 新能源2402 新能源2403 新能源2404 材控2401 材控2402 材控2403 材控2404 日语2401 英语2401 英语2402 英语2403 英语2404</t>
+          <t>工商类2401 工商类2402 工商类2403 工商类2404 工商类2405 工商类2406 工商类2407 工商类2408 工商类2409 工商类2410 工商类2411 工商类2412 工业2401 工业2402 工业2403 旅游2401 旅游2402</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>周四（3-4节）</t>
+          <t>周三（3-4节）</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>周四</t>
+          <t>周三</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>第7-8节</t>
+          <t>第5-6节</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -911,43 +911,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>15200002.009</t>
+          <t>150000290.117</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>体育与健康2</t>
+          <t>体育与健康4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>计算机科学与技术学院 资源环境学院 资源环境学院</t>
+          <t>计算机科学与技术学院 能源科学与工程学院</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>新笑莉</t>
+          <t>新瑞青</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>xkp01960015</t>
+          <t>xkp01050063</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(共占)</t>
+          <t>501</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>(共占)</t>
+          <t>CLS1021</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>机器感知与机器视觉2501 机器感知与机器视觉2502 计算机2501 计算机2502 计算机2503 计算机2504 计算机2505 计算机2506 计实验2501 物联网2501 物联网2502 物联网2503 物联网2504 地质2501 地质2502 地质卓2501 环境2501 环境2502 环境2503 环境2504 水文2501 水文2502 水文2503 资源环境大数据工程2501 资源环境大数据工程2502 资源环境大数据工程2503 地质2503 勘查拔尖班2501 勘查清洁2501 勘查清洁2502 勘查战略2501 勘查战略2502</t>
+          <t>计算机2401 计算机2402 计算机2403 计算机2404 计算机2405 计实验2401 物联网2401 物联网2402 物联网2403 智采2401 智采2402 智采2403 采矿卓2401 采矿卓2402 新能科2401 新能科2402 交通2401 交通2402 交通2403 机器感知与机器视觉2401 机器感知与机器视觉2402</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>周二（3-4节）</t>
+          <t>周三（3-4节）</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -977,58 +977,58 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>周一</t>
+          <t>周三</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>第3-4节</t>
+          <t>第5-6节</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>15200002.084</t>
+          <t>150000290.118</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>体育与健康2</t>
+          <t>体育与健康4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>机械与动力工程学院</t>
+          <t>计算机科学与技术学院 能源科学与工程学院</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>新军鹏</t>
+          <t>新清华</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>xkp01050038</t>
+          <t>xkp01050044</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(共占)</t>
+          <t>401</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>(共占)</t>
+          <t>CLS1022</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>测控2501 测控2502 测控2503 测控2504 车辆2501 车辆2502 车辆2503 机械2501 机械2502 机械2503 机械2504 机械2505 机械2506 机械2507 机械2508 机械2509 机械2510 机械2511 机械2512 能动2501 能动2502 能动2503 能动2504 智能制造2501 智能制造2502 智能制造2503 智能制造2504</t>
+          <t>计算机2401 计算机2402 计算机2403 计算机2404 计算机2405 计实验2401 物联网2401 物联网2402 物联网2403 智采2401 智采2402 智采2403 采矿卓2401 采矿卓2402 新能科2401 新能科2402 交通2401 交通2402 交通2403 机器感知与机器视觉2401 机器感知与机器视觉2402</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>周四（3-4节）</t>
+          <t>周三（3-4节）</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>周四</t>
+          <t>周三</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1073,27 +1073,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>15200002.086</t>
+          <t>150000290.134</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>体育与健康2</t>
+          <t>体育与健康4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>机械与动力工程学院</t>
+          <t>软件学院</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>新丽君</t>
+          <t>新燕桐</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>xkp01050006</t>
+          <t>xkp01170064</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1104,27 +1104,27 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(共占)</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>(共占)</t>
+          <t>CLS1013</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>南校区</t>
+          <t>北校区</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>测控2501 测控2502 测控2503 测控2504 车辆2501 车辆2502 车辆2503 机械2501 机械2502 机械2503 机械2504 机械2505 机械2506 机械2507 机械2508 机械2509 机械2510 机械2511 机械2512 能动2501 能动2502 能动2503 能动2504 智能制造2501 智能制造2502 智能制造2503 智能制造2504</t>
+          <t>网安2401 网安2402 网安2403 网安2404 网安2405 网安2406 网安2407 网安2408</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>周四（3-4节）</t>
+          <t>周三（5-6节）</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>周四</t>
+          <t>周三</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>第5-6节</t>
+          <t>第7-8节</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -1154,82 +1154,1864 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>150000290.135</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>体育与健康4</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>软件学院</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>新新锋</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>xkp01050013</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>41</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2306</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>CLS1014</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>北校区</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>网安2401 网安2402 网安2403 网安2404 网安2405 网安2406 网安2407 网安2408</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>周三（5-6节）</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>周二(5-8节）;全周（1-2节）</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>周三</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>第7-8节</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>150000290.136</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>体育与健康4</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>软件学院</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>新红</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>xkp01050020</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>40</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2407</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>CLS1017</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>北校区</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>网安2401 网安2402 网安2403 网安2404 网安2405 网安2406 网安2407 网安2408</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>周三（5-6节）</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>周二(5-8节）;全周（1-2节）</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>周三</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>第7-8节</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>150000290.139</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>体育与健康4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>测绘与国土信息工程学院</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>新玉真</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>xkp01050058</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>45</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2310</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>CLS1015</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>测绘卓2401 测绘卓2402 测绘卓2403 测绘卓2404 测绘2401 测绘2402 测绘2403 测绘2404 遥感2401 遥感2402 遥感2403 遥感2404 土管2401 土管2402 地信2401 地信2402 地信2403 自环2401 城乡2401 城乡2402</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>周二（3-4节）</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>周二(5-8节）;全周（1-2节）</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>第3-4节</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>150000290.149</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>体育与健康4</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>测绘与国土信息工程学院</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>新晨阳</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>xkp01231126</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>45</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>CLS1009</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>测绘卓2401 测绘卓2402 测绘卓2403 测绘卓2404 测绘2401 测绘2402 测绘2403 测绘2404 遥感2401 遥感2402 遥感2403 遥感2404 土管2401 土管2402 地信2401 地信2402 地信2403 自环2401 城乡2401 城乡2402</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>周四（3-4节）</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>周二(5-8节）;全周（1-2节）</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>第5-6节</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>150000290.160</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>体育与健康4</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>化学化工学院 资源环境学院 资源环境学院</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>新瑞青</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>xkp01050063</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>46</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2403</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>CLS1016</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>矿加2401 矿加卓2401 矿加卓2402 应化2401 应化2402 应化2403 化工2401 化工2402 化工2403 化工2404 储能2401 储能2402 储能2403 地质2401 地质2402 地质卓2401 地科2401 地科2402 地科2403 水文2401 水文2402 水文2403 勘查拔尖班2401 勘查清洁2401 勘查清洁2402 勘查战略2401 勘查战略2402 环境2401 环境2402 环境生态2401 环境生态2402</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>周四（3-4节）</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>周二(5-8节）;全周（1-2节）</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>第5-6节</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>150000290.173</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>体育与健康4</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>化学化工学院 资源环境学院 资源环境学院</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>新娜娜</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>xkp01230661</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>45</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>CLS1009</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>矿加2401 矿加卓2401 矿加卓2402 应化2401 应化2402 应化2403 化工2401 化工2402 化工2403 化工2404 储能2401 储能2402 储能2403 地质2401 地质2402 地质卓2401 地科2401 地科2402 地科2403 水文2401 水文2402 水文2403 勘查拔尖班2401 勘查清洁2401 勘查清洁2402 勘查战略2401 勘查战略2402 环境2401 环境2402 环境生态2401 环境生态2402</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>周四（5-6节）</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>周二(5-8节）;全周（1-2节）</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>第7-8节</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>150000290.180</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>体育与健康4</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>数学与信息科学学院 安全科学与工程学院</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>新真</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>xkp01050036</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>43</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2306</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>CLS1014</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>安全卓2401 安全卓2402 安全卓2403 安全卓2404 安全卓2405 安全卓2406 安全卓2407 安全卓2408 安全卓2409 消防2401 消防2402 数学类2401 数学类2402 数学类2403 数学类2404 数学类2405 数学类2406 数学类2407</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>周四（5-6节）</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>周二(5-8节）;全周（1-2节）</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>第7-8节</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>150000290.194</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>体育与健康4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>物理与电子信息学院</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>新俊魁</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>xkp01050057</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>40</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>CLS1006</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>电信2401 电信2402 人工智能2401 人工智能2402 人工智能2403 微电子2401 微电子2402 微电子2403 通信2401 通信2402 通信2403 通信2404 电信合2401 电信合2402 电信合2403 电信合2404 物理2401 物理2402</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>周五（3-4节）</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>周二(5-8节）;全周（1-2节）</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>第7-8节</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>150000290.204</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>体育与健康4</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>物理与电子信息学院</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>新骞</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>xkp01120077</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>40</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>402</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>CLS1031</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>电信2401 电信2402 人工智能2401 人工智能2402 人工智能2403 微电子2401 微电子2402 微电子2403 通信2401 通信2402 通信2403 通信2404 电信合2401 电信合2402 电信合2403 电信合2404 物理2401 物理2402</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>周一（5-6节）</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>周二(5-8节）;全周（1-2节）</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>第3-4节</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>150000290.218</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>体育与健康4</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>外国语学院 材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>新真</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>xkp01050036</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>43</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>CLS1009</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>材科2401 材科2402 材科2403 材科2404 材科2405 材科2406 材科2407 材科2408 材科2409 材科2410 智能材料2401 智能材料2402 新能源2401 新能源2402 新能源2403 新能源2404 材控2401 材控2402 材控2403 材控2404 日语2401 英语2401 英语2402 英语2403 英语2404</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>周五（3-4节）</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>周二(5-8节）;全周（1-2节）</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>第7-8节</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>150000290.220</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>体育与健康4</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>外国语学院 材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>新建平</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>xkp01050048</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>43</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2407</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>CLS1017</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>材科2401 材科2402 材科2403 材科2404 材科2405 材科2406 材科2407 材科2408 材科2409 材科2410 智能材料2401 智能材料2402 新能源2401 新能源2402 新能源2403 新能源2404 材控2401 材控2402 材控2403 材控2404 日语2401 英语2401 英语2402 英语2403 英语2404</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>周一（3-4节）</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>周二(5-8节）;全周（1-2节）</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>第5-6节</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>150000290.221</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>体育与健康4</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>外国语学院 材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>新衍榛</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>xkp01050012</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>43</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2403</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>CLS1016</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>材科2401 材科2402 材科2403 材科2404 材科2405 材科2406 材科2407 材科2408 材科2409 材科2410 智能材料2401 智能材料2402 新能源2401 新能源2402 新能源2403 新能源2404 材控2401 材控2402 材控2403 材控2404 日语2401 英语2401 英语2402 英语2403 英语2404</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>周四（3-4节）</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>周二(5-8节）;全周（1-2节）</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>第7-8节</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>150000290.226</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>体育与健康4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>外国语学院 材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>新达</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>xkp01230328</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>43</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2306</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>CLS1014</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>材科2401 材科2402 材科2403 材科2404 材科2405 材科2406 材科2407 材科2408 材科2409 材科2410 智能材料2401 智能材料2402 新能源2401 新能源2402 新能源2403 新能源2404 材控2401 材控2402 材控2403 材控2404 日语2401 英语2401 英语2402 英语2403 英语2404</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>周一（3-4节）</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>周二(5-8节）;全周（1-2节）</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>第7-8节</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>15200002.009</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>体育与健康2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>计算机科学与技术学院 资源环境学院 资源环境学院</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>新笑莉</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>xkp01960015</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>46</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(共占)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>(共占)</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>机器感知与机器视觉2501 机器感知与机器视觉2502 计算机2501 计算机2502 计算机2503 计算机2504 计算机2505 计算机2506 计实验2501 物联网2501 物联网2502 物联网2503 物联网2504 地质2501 地质2502 地质卓2501 环境2501 环境2502 环境2503 环境2504 水文2501 水文2502 水文2503 资源环境大数据工程2501 资源环境大数据工程2502 资源环境大数据工程2503 地质2503 勘查拔尖班2501 勘查清洁2501 勘查清洁2502 勘查战略2501 勘查战略2502</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>周二（3-4节）</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>周二(5-8节）;全周（1-2节）</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>第3-4节</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>15200002.080</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>体育与健康2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>软件学院</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>新燕桐</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>xkp01170064</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>49</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(共占)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>(共占)</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>北校区</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>网安2501 网安2502 网安2503 网安2504 网安2505 网安2506 网安2507 网安2508</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>周四（3-4节）</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>周二(5-8节）;全周（1-2节）</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>第5-6节</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>15200002.081</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>体育与健康2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>软件学院</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>新新新</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>xkp01170079</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="n">
+        <v>49</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(共占)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>(共占)</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>北校区</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>网安2501 网安2502 网安2503 网安2504 网安2505 网安2506 网安2507 网安2508</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>周四（3-4节）</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>周二(5-8节）;全周（1-2节）</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>第5-6节</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>15200002.082</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>体育与健康2</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>软件学院</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>新红</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>xkp01050020</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" t="n">
+        <v>49</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(共占)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>(共占)</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>北校区</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>网安2501 网安2502 网安2503 网安2504 网安2505 网安2506 网安2507 网安2508</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>周四（3-4节）</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>周二(5-8节）;全周（1-2节）</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>第5-6节</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>15200002.083</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>体育与健康2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>软件学院</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>新刚</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>xkp01230325</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" t="n">
+        <v>49</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(共占)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>(共占)</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>北校区</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>网安2501 网安2502 网安2503 网安2504 网安2505 网安2506 网安2507 网安2508</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>周四（3-4节）</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>周二(5-8节）;全周（1-2节）</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>第5-6节</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>15200002.084</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>体育与健康2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>机械与动力工程学院</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>新军鹏</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>xkp01050038</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" t="n">
+        <v>42</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(共占)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>(共占)</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>测控2501 测控2502 测控2503 测控2504 车辆2501 车辆2502 车辆2503 机械2501 机械2502 机械2503 机械2504 机械2505 机械2506 机械2507 机械2508 机械2509 机械2510 机械2511 机械2512 能动2501 能动2502 能动2503 能动2504 智能制造2501 智能制造2502 智能制造2503 智能制造2504</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>周四（3-4节）</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>周二(5-8节）;全周（1-2节）</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>第5-6节</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>15200002.086</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>体育与健康2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>机械与动力工程学院</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>新丽君</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>xkp01050006</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" t="n">
+        <v>41</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(共占)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>(共占)</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>测控2501 测控2502 测控2503 测控2504 车辆2501 车辆2502 车辆2503 机械2501 机械2502 机械2503 机械2504 机械2505 机械2506 机械2507 机械2508 机械2509 机械2510 机械2511 机械2512 能动2501 能动2502 能动2503 能动2504 智能制造2501 智能制造2502 智能制造2503 智能制造2504</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>周四（3-4节）</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>周二(5-8节）;全周（1-2节）</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>第5-6节</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>151130890.001</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>体育基本理论</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>体育学院</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>新新海</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>xkp01050035</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" t="n">
+      <c r="F30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" t="n">
         <v>82</v>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>CLS1005</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>CLS1012</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
         <is>
           <t>南校区</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>体育2301 体育2302 体育2303</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>周二（3-4节）</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>周二(5-8节）</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>周五</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>第3-4节</t>
         </is>
       </c>
-      <c r="Q10" t="n">
-        <v>2</v>
+      <c r="Q30" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>150013340.003</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>副项2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>体育学院</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>新燕</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>xkp01050008</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" t="n">
+        <v>16</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>CLS1022</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>体育2301 体育2302 体育23033</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>周一（3-4节）</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>第5-6节</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>150130140.001</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>网球</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>体育学院</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>新枫</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>xkp01050026</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" t="n">
+        <v>41</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2310</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>CLS1015</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>民传2301</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>周一（3-4节）</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>第7-8节</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/排课结果/软偏好修复明细.xlsx
+++ b/排课结果/软偏好修复明细.xlsx
@@ -537,12 +537,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>301</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CLS1006</t>
+          <t>CLS1005</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -618,12 +618,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2205</t>
+          <t>301</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CLS1010</t>
+          <t>CLS1005</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -699,12 +699,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2203</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CLS1009</t>
+          <t>CLS1006</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2306</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CLS1014</t>
+          <t>CLS1006</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2403</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CLS1016</t>
+          <t>CLS1006</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>2205</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CLS1021</t>
+          <t>CLS1010</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>2403</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CLS1022</t>
+          <t>CLS1016</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>301</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CLS1013</t>
+          <t>CLS1005</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2306</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CLS1014</t>
+          <t>CLS1006</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2407</t>
+          <t>2106</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CLS1017</t>
+          <t>CLS1008</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2203</t>
+          <t>301</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CLS1009</t>
+          <t>CLS1005</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2403</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CLS1016</t>
+          <t>CLS1006</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1590,12 +1590,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2203</t>
+          <t>301</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>CLS1009</t>
+          <t>CLS1005</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2306</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CLS1014</t>
+          <t>CLS1006</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1752,12 +1752,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>301</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>CLS1006</t>
+          <t>CLS1005</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2203</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>CLS1009</t>
+          <t>CLS1006</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2407</t>
+          <t>2203</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CLS1017</t>
+          <t>CLS1009</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2076,12 +2076,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2403</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>CLS1016</t>
+          <t>CLS1007</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2157,12 +2157,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2306</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CLS1014</t>
+          <t>CLS1006</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>CLS1012</t>
+          <t>CLS1007</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2886,12 +2886,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>2306</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>CLS1022</t>
+          <t>CLS1014</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2967,12 +2967,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>2203</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>CLS1015</t>
+          <t>CLS1009</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
